--- a/results/Int Task Remove ACC -1.0/Rando_2_permute.xlsx
+++ b/results/Int Task Remove ACC -1.0/Rando_2_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6894382151908456</v>
+        <v>0.7209106268894303</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6894382151908456</v>
+        <v>0.732700672340485</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6829253094651297</v>
+        <v>0.7287680390418276</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6699719334501609</v>
+        <v>0.7185284610175171</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6564617645621409</v>
+        <v>0.6964094714133113</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6569506601224595</v>
+        <v>0.690457896684377</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6444929868534046</v>
+        <v>0.6935225265480238</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6444929868534046</v>
+        <v>0.699509184464257</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6406259818056147</v>
+        <v>0.7011116657706782</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6545548798793557</v>
+        <v>0.7039397895706935</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.662773247411524</v>
+        <v>0.7059938141882693</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6600198281098366</v>
+        <v>0.7078837681786765</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.658312097241519</v>
+        <v>0.7272425312955995</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.658312097241519</v>
+        <v>0.7320194301512941</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6748868959931859</v>
+        <v>0.7331680990846954</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.678891964728306</v>
+        <v>0.7275448401533187</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6453114200138238</v>
+        <v>0.6940671013956476</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6787472683986009</v>
+        <v>0.6940671013956476</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6775635162779008</v>
+        <v>0.6853383694870524</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6684488693090183</v>
+        <v>0.7064003253485629</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6624871710733011</v>
+        <v>0.6875418031012839</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6599793340827056</v>
+        <v>0.668145687735197</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6637478967541943</v>
+        <v>0.6702653406036403</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6605474722650823</v>
+        <v>0.6827116685633696</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6526097702313046</v>
+        <v>0.665841542682799</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6524366233566756</v>
+        <v>0.6220065837702732</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6516014340470988</v>
+        <v>0.6209427428419826</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6515176533013105</v>
+        <v>0.6209427428419826</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6455219191376168</v>
+        <v>0.610359140130279</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6044244960937227</v>
+        <v>0.6052099405854878</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6198019283534989</v>
+        <v>0.6052099405854878</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6217484343473131</v>
+        <v>0.6071983369521962</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.606769309716472</v>
+        <v>0.6108876570016267</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.606769309716472</v>
+        <v>0.6108876570016267</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6118450265654781</v>
+        <v>0.6125999259936745</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5854392554684391</v>
+        <v>0.6249874328881317</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6186872953480741</v>
+        <v>0.6252658293246574</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6237968735818363</v>
+        <v>0.6939833206498593</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6127662656827084</v>
+        <v>0.6788310491443892</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5975766419280742</v>
+        <v>0.6797295976429684</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5975766419280742</v>
+        <v>0.6817813531986791</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5985024191690347</v>
+        <v>0.6701939524264999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5797039397895707</v>
+        <v>0.66619795993884</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5787748462274228</v>
+        <v>0.6702166430451508</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5798657413548743</v>
+        <v>0.6702166430451508</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5831996914075863</v>
+        <v>0.6803464333838345</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5760179360613276</v>
+        <v>0.7123766852147928</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6137417877414806</v>
+        <v>0.6289607347571405</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6132132708701328</v>
+        <v>0.6282986923221928</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.629465513750515</v>
+        <v>0.6181757091691045</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6280316411949927</v>
+        <v>0.6188332134803221</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5801191781108839</v>
+        <v>0.5440487743575064</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5833897689745935</v>
+        <v>0.5354422227031858</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.612471985813127</v>
+        <v>0.5319520564682226</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5949420865594739</v>
+        <v>0.5319520564682226</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5793869693013385</v>
+        <v>0.5397234188129665</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5722018976338921</v>
+        <v>0.535563355698138</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5700799757035837</v>
+        <v>0.5358417521346636</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5787758934867452</v>
+        <v>0.536782191006137</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5654502167826797</v>
+        <v>0.5367120246315392</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5657727726539645</v>
+        <v>0.5328801027710481</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5638217285364202</v>
+        <v>0.5355282725108391</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5335999190119457</v>
+        <v>0.5259247299816381</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5344724605706865</v>
+        <v>0.5483231632816918</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5376728850597985</v>
+        <v>0.5346613163351509</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5255309604764332</v>
+        <v>0.5353912560828312</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5276087229719824</v>
+        <v>0.4959167359021441</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4862723502593712</v>
+        <v>0.5047903386836649</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4883942721896796</v>
+        <v>0.5126760268377656</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4594375519266081</v>
+        <v>0.5188335625667627</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4606190349854431</v>
+        <v>0.5260627936689684</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4787160251621506</v>
+        <v>0.5338205416425215</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4651786275317494</v>
+        <v>0.521847225810055</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4585616940466798</v>
+        <v>0.5104443172218305</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4585616940466798</v>
+        <v>0.5102010039726037</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4647770035816269</v>
+        <v>0.5149834882113509</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4618108160942813</v>
+        <v>0.5312233385230851</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4611533117830637</v>
+        <v>0.5312233385230851</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4691498348821135</v>
+        <v>0.5329265312676725</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4779770091670099</v>
+        <v>0.5507325578959862</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4639222654313661</v>
+        <v>0.5025994721813015</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.462396757685138</v>
+        <v>0.5158809894506078</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.462396757685138</v>
+        <v>0.5158809894506078</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4636834903058695</v>
+        <v>0.5167535310093485</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4575168783294119</v>
+        <v>0.5083100027228743</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4679419957969992</v>
+        <v>0.5041340561749901</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4679725408605679</v>
+        <v>0.5040989729876912</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.498025567090923</v>
+        <v>0.5028167784906898</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4978875034035928</v>
+        <v>0.5013195467461653</v>
       </c>
     </row>
   </sheetData>
